--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/AI/Artifacts/1. Stakeholder Register_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/AI/Artifacts/1. Stakeholder Register_VNS.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stakeholder register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stakeholder register'!$B$10:$N$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stakeholder register'!$B$10:$N$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -523,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:N29"/>
+  <dimension ref="B2:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>V1.1</t>
+          <t>V1.2</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>Funds the project and owns the current VNS platform and the student data. Approves scope and accepts the final result. Main interest is replacing the outdated Moodle-based platform and gaining engagement analytics.</t>
+          <t>Funds the project, owns the current VNS platform and the student data, and represents the university leadership: approves the project charter and MVP scope and accepts the final result. Main interest is replacing the outdated Moodle-based platform and gaining engagement analytics.</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Meet their needs</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -888,14 +888,14 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
           <t>10 Peremohy Avenue, Kyiv, 01135, Ukraine</t>
@@ -913,49 +913,49 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Monitoring of national regulation</t>
+          <t>Official one-page report</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Ad hoc, if regulation changes</t>
+          <t>Once per semester and at control points</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Formal sponsor of the sector, but for a pilot inside a single department the ministry has neither influence over delivery nor day-to-day interest in it. Monitored only in case the national regulation of educational IT systems changes; no recurring communication and no project activity is assigned to it.</t>
+          <t>Sets the regulatory framework for educational IT systems and for processing personal data in education, and can condition the scaling of the product beyond the pilot. Not involved in day-to-day work: kept satisfied through formal semester reporting and consulted only on decisions with regulatory impact.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="74" customHeight="1">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nataliia Shakhovska</t>
+          <t>Technical Department of Lviv Polytechnic</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>External / Primary</t>
+          <t>External / Secondary</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Meet their needs</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Rector's Office, Lviv Polytechnic National University</t>
+          <t>Lviv Polytechnic National University</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Rector of Lviv Polytechnic National University</t>
+          <t>Developers and administrators of the current VNS</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -970,34 +970,34 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>+380 (32) 258-26-00</t>
+          <t>+380 (32) 258-21-77</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>nataliia.b.shakhovska@lpnu.ua</t>
+          <t>it.support@lpnu.ua</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>E-mail with a one-page summary</t>
+          <t>E-mail / ticket on request</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Once per semester and at control points</t>
+          <t>As needed (registry export, infrastructure access)</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Highest decision-making authority in the university: approves the project charter and is the person who can authorise scaling the product beyond the pilot. Not involved day to day — summary communication only.</t>
+          <t>Built and maintain the current VNS. Because the project uses its own custom backend with no Moodle integration, the department neither controls delivery nor depends on its result. Involvement is limited to one-off requests: the export of the student registry and access to university infrastructure. Monitored in case they react to the replacement of their system.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="74" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Nataliia Boiko</t>
+          <t>End users — students and lecturers</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1007,198 +1007,198 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
+          <t>Keep Informed</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Students and teaching staff of Lviv Polytechnic National University</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>End users of the product: students and lecturers</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>12 S. Bandery Street, Lviv, 79013, Ukraine</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Via learning channels and @lpnu.ua mailboxes</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Interviews, surveys, usability tests, demos</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Weekly during elicitation and the pilot</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Primary target audience in two roles. Students: scattered chats, misleading grade summary, empty calendar. Lecturers: course materials, assignments, activity analytics and the AI mode for graded work. No direct influence on decisions, but requirements not validated with them will be wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="74" customHeight="1">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Kostiantyn Holovskyi</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Internal / Primary</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
           <t>Key Player</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Lviv Polytechnic National University</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Lecturer — customer and end user</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Project team “20/80”</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>12 S. Bandery Street, Lviv, 79013, Ukraine</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>+380 (32) 258-25-30</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>nataliia.i.boiko@lpnu.ua</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>Interview, requirements workshop, increment demo</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>Weekly, Thursday</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>Dual role: defines and accepts requirements while also being a future user of the product. Key source of lecturer-facing requirements — course materials, assignments, activity analytics, and the AI mode for graded work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="74" customHeight="1">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Technical Department of Lviv Polytechnic</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>External / Primary</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Key Player</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Lviv Polytechnic National University</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Developers and administrators of the current VNS</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>5 Lukasha Street, Lviv, Ukraine</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>+380 (67) 000-00-01</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>kostiantyn.holovskyi.shi.2025@lpnu.ua</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Team meeting + backlog</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>Weekly, Monday</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>Owns the product vision and backlog priorities. Approves the MVP scope and accepts the result from the product side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="74" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Nazar Zankovych</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Internal / Primary</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Meet their needs</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Project team “20/80”</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>12 S. Bandery Street, Lviv, 79013, Ukraine</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>+380 (32) 258-21-77</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>it.support@lpnu.ua</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>Working meeting + e-mail</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>Every two weeks</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>Own the current VNS, the infrastructure and the student registry, without which registration cannot work. Risk of resistance: the project replaces the system they built — engage them as partners rather than as a supplier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="74" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>End users — Lviv Polytechnic students</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>External / Primary</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Keep Informed</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Student body of Lviv Polytechnic National University</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>End users of the product</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>12 S. Bandery Street, Lviv, 79013, Ukraine</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>Via learning channels and @lpnu.ua mailboxes</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>Survey, usability test, announcement</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>Weekly during the pilot</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>Primary target audience. Source of evidence on the real pain points: scattered chats, misleading grade summary, empty calendar. No direct influence on decisions, but requirements not validated with them will be wrong.</t>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>5 Lukasha Street, Lviv, Ukraine</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>+380 (67) 000-00-02</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>nazar.zankovych.shi.2025@lpnu.ua</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>All project ceremonies</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>High authority over the plan, schedule, resources and communications. Interest is in delivering on time and within scope rather than in the functional content of the product, which is owned by the Product Owner. Single point of contact for the sponsors.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="74" customHeight="1">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Kostiantyn Holovskyi</t>
+          <t>Andrii Lysun</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Product Owner</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
@@ -1238,34 +1238,34 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>+380 (67) 000-00-01</t>
+          <t>+380 (67) 000-00-03</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>kostiantyn.holovskyi.shi.2025@lpnu.ua</t>
+          <t>andrii.lysun.shi.2025@lpnu.ua</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>Team meeting + backlog</t>
+          <t>Requirements elicitation meetings, workshops</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>Weekly, Monday</t>
+          <t>Weekly + as needed</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>Owns the product vision and backlog priorities. Approves the MVP scope and accepts the result from the product side.</t>
+          <t>Elicits and documents requirements and produces the BA artifacts and UML models. Main contact for the end users — both students and lecturers.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="74" customHeight="1">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Nazar Zankovych</t>
+          <t>Denys Lunhul</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Tech Lead, Software Engineer (SWE)</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -1305,44 +1305,44 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>+380 (67) 000-00-02</t>
+          <t>+380 (67) 000-00-04</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>nazar.zankovych.shi.2025@lpnu.ua</t>
+          <t>denys.lunhul.shi.2025@lpnu.ua</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>All project ceremonies</t>
+          <t>Technical sync + code review</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly, Tuesday</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Responsible for the plan, schedule and communications. Single point of contact for the sponsors, the Rector's office and the Technical Department.</t>
+          <t>Software engineer who also leads the technical side: owns the custom backend architecture, decides on the technology stack and is accountable for the technical feasibility of requirements.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="74" customHeight="1">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Andrii Lysun</t>
+          <t>Yaroslav Shevchuk</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Internal / Primary</t>
+          <t>Internal / Secondary</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Key Player</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>DevOps, Software Engineer (SWE)</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -1372,44 +1372,44 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>+380 (67) 000-00-03</t>
+          <t>+380 (67) 000-00-05</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>andrii.lysun.shi.2025@lpnu.ua</t>
+          <t>yaroslav.shevchuk.shi.2025@lpnu.ua</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>Requirements elicitation meetings, workshops</t>
+          <t>Daily stand-up + technical sync</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>Weekly + as needed</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>Elicits and documents requirements and produces the BA artifacts and UML models. Main contact for Nataliia Boiko and the end users.</t>
+          <t>Software engineer who also owns deployment, environments and CI/CD. Low influence: executes tasks agreed in planning and does not set scope or priorities. Low interest in the business outcome: engagement is at task level. Kept in the loop through the team's own ceremonies, so no separate stakeholder communication is needed.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="74" customHeight="1">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Denys Lunhul</t>
+          <t>Volodymyr Kamelchuk</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Internal / Primary</t>
+          <t>Internal / Secondary</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Key Player</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
+          <t>QA Specialist, Software Engineer (SWE)</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -1439,235 +1439,101 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>+380 (67) 000-00-04</t>
+          <t>+380 (67) 000-00-06</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>denys.lunhul.shi.2025@lpnu.ua</t>
+          <t>volodymyr.kamelchuk.shi.2025@lpnu.ua</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>Technical sync + code review</t>
+          <t>Daily stand-up + defect report</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>Weekly, Tuesday</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>Responsible for the custom backend architecture and the technical feasibility of requirements. Decides on the technology stack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="74" customHeight="1">
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Yaroslav Shevchuk</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Internal / Secondary</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Keep Informed</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Project team “20/80”</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>DevOps</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>5 Lukasha Street, Lviv, Ukraine</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>+380 (67) 000-00-05</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>yaroslav.shevchuk.shi.2025@lpnu.ua</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>Daily stand-up + technical sync</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>Deployment, environments, CI/CD, queue and workers for AI tasks. Main contact with the university Technical Department.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="74" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Volodymyr Kamelchuk</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Internal / Secondary</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Keep Informed</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Project team “20/80”</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>QA Specialist</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>5 Lukasha Street, Lviv, Ukraine</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>+380 (67) 000-00-06</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>volodymyr.kamelchuk.shi.2025@lpnu.ua</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>Daily stand-up + defect report</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>Verifies the acceptance criteria, in particular the correctness of the grade forecast and the AI's refusal to produce complete solutions for graded work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="9" t="inlineStr">
+          <t>Software engineer who also verifies the acceptance criteria, in particular the grade forecast and the AI's refusal to produce complete solutions for graded work. Low influence and low interest in the business outcome; kept in the loop through the team's own ceremonies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>LEGEND AND COMPLETION RULES</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="24" ht="32" customHeight="1">
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Internal — a member of the delivery team; External — a stakeholder on the university or state side. Primary — directly involved; Secondary — involved indirectly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Stakeholder Group</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Derived from Power/Influence × Interest: High+High = Key Player (ENGAGE); High+Low = Meet their needs (SATISFY); Low+High = Keep Informed (INFORM); Low+Low = Monitor (MONITOR).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>MONITOR quadrant</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Internal — a member of the delivery team; External — a stakeholder on the university or state side. Primary — directly involved; Secondary — involved indirectly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
+          <t>The Technical Department, DevOps and QA sit here. The department only handles one-off requests because the custom backend does not depend on the current VNS; DevOps and QA execute agreed tasks and are kept in the loop through the team's own ceremonies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Stakeholder Group</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Derived from Power/Influence × Interest: High+High = Key Player (ENGAGE); High+Low = Meet their needs (SATISFY); Low+High = Keep Informed (INFORM); Low+Low = Monitor (MONITOR).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>MONITOR quadrant</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>The Ministry of Education and Science sits here: for a pilot inside a single department it has neither influence over delivery nor day-to-day interest, so it carries no RACI column and no recurring communication.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
           <t>Phone numbers are illustrative placeholders for this training project. Team e-mail addresses follow the real Lviv Polytechnic National University format.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B10:N23"/>
+  <autoFilter ref="B10:N21"/>
   <mergeCells count="16">
-    <mergeCell ref="C26:N26"/>
     <mergeCell ref="I7:N7"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C24:N24"/>
+    <mergeCell ref="B23:N23"/>
     <mergeCell ref="I5:N5"/>
     <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C25:N25"/>
     <mergeCell ref="C27:N27"/>
-    <mergeCell ref="C28:N28"/>
-    <mergeCell ref="C29:N29"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="I8:N8"/>
-    <mergeCell ref="B25:N25"/>
+    <mergeCell ref="C26:N26"/>
     <mergeCell ref="I4:N4"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="I6:N6"/>
